--- a/backend/assets/report-templates/leave-summary-report.xlsx
+++ b/backend/assets/report-templates/leave-summary-report.xlsx
@@ -286,32 +286,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -600,153 +604,155 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
-  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="12" style="0" width="3.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="12" style="1" width="3.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="8.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="15"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="16"/>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:S1"/>

--- a/backend/assets/report-templates/leave-summary-report.xlsx
+++ b/backend/assets/report-templates/leave-summary-report.xlsx
@@ -28,13 +28,13 @@
     <t xml:space="preserve">員工資料</t>
   </si>
   <si>
-    <t xml:space="preserve">2025年到職日前可請休天數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025年到職日後可請休天數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01假況(時)</t>
+    <t xml:space="preserve">2026年到職日前可請休天數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年到職日後可請休天數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06假況(時)</t>
   </si>
   <si>
     <t xml:space="preserve">員工編號</t>
@@ -43,10 +43,12 @@
     <t xml:space="preserve">姓名</t>
   </si>
   <si>
-    <t xml:space="preserve">到職日前應休天數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">剩餘應修時數</t>
+    <t xml:space="preserve">到職日前
+應休天數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">剩餘
+應修時數</t>
   </si>
   <si>
     <t xml:space="preserve">起</t>
@@ -55,10 +57,12 @@
     <t xml:space="preserve">迄</t>
   </si>
   <si>
-    <t xml:space="preserve">到職日後應休天數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特休總時數</t>
+    <t xml:space="preserve">到職日後
+應休天數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特休
+總時數</t>
   </si>
   <si>
     <t xml:space="preserve">休餘</t>
@@ -89,8 +93,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -189,7 +194,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5D9F1"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
     <fill>
@@ -199,58 +204,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -286,12 +245,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -307,51 +266,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -380,7 +319,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF31869B"/>
-      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -602,22 +541,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="12" style="1" width="3.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="7.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="8.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="12" style="1" width="4.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="4.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -643,7 +580,7 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -672,87 +609,380 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="16"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:S1"/>
@@ -762,8 +992,8 @@
     <mergeCell ref="K2:S2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.472222222222222" right="0.472222222222222" top="0.472222222222222" bottom="0.472222222222222" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/backend/assets/report-templates/leave-summary-report.xlsx
+++ b/backend/assets/report-templates/leave-summary-report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t xml:space="preserve">臺龍電子股份有限公司 特休表</t>
   </si>
@@ -34,10 +34,11 @@
     <t xml:space="preserve">2026年到職日後可請休天數</t>
   </si>
   <si>
-    <t xml:space="preserve">06假況(時)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">員工編號</t>
+    <t xml:space="preserve">假況(時)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">員工
+編號</t>
   </si>
   <si>
     <t xml:space="preserve">姓名</t>
@@ -65,10 +66,24 @@
 總時數</t>
   </si>
   <si>
-    <t xml:space="preserve">休餘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特休</t>
+    <t xml:space="preserve">特休
+休餘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特休
+已休</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返台假
+總時數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返台假
+休餘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返台假
+已休</t>
   </si>
   <si>
     <t xml:space="preserve">病假</t>
@@ -97,7 +112,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +170,13 @@
       <b val="true"/>
       <sz val="8"/>
       <color rgb="FF31869B"/>
+      <name val="微軟正黑體"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="7"/>
       <name val="微軟正黑體"/>
       <family val="0"/>
       <charset val="1"/>
@@ -254,6 +276,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -267,10 +293,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -282,7 +304,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -290,7 +312,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -543,77 +565,83 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:V19"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="7.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="12" style="1" width="4.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="4.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="6.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="7.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="7.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="5.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="2" width="5.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="17" style="1" width="4.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="4.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -622,10 +650,10 @@
       <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -634,41 +662,50 @@
       <c r="H3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
@@ -688,8 +725,11 @@
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
@@ -709,8 +749,11 @@
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
       <c r="S5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
@@ -730,8 +773,11 @@
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
@@ -751,8 +797,11 @@
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
@@ -772,8 +821,11 @@
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
@@ -793,8 +845,11 @@
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
@@ -814,8 +869,11 @@
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
@@ -835,8 +893,11 @@
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
@@ -856,8 +917,11 @@
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
@@ -877,8 +941,11 @@
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
@@ -898,8 +965,11 @@
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
@@ -919,8 +989,11 @@
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
@@ -940,8 +1013,11 @@
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
@@ -961,8 +1037,11 @@
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8"/>
@@ -982,17 +1061,21 @@
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
-    </row>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="K2:V2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.472222222222222" right="0.472222222222222" top="0.472222222222222" bottom="0.472222222222222" header="0.511811023622047" footer="0.511811023622047"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/backend/assets/report-templates/leave-summary-report.xlsx
+++ b/backend/assets/report-templates/leave-summary-report.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
-    <t xml:space="preserve">臺龍電子股份有限公司 特休表</t>
+    <t xml:space="preserve">臺龍電子股份有限公司 請假總表</t>
   </si>
   <si>
     <t xml:space="preserve">員工資料</t>
